--- a/artfynd/A 29934-2025 artfynd.xlsx
+++ b/artfynd/A 29934-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ113"/>
+  <dimension ref="A1:AZ114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1453,7 +1453,7 @@
         <v>136361109</v>
       </c>
       <c r="B9" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>136361119</v>
       </c>
       <c r="B10" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>136361120</v>
       </c>
       <c r="B11" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>136361122</v>
       </c>
       <c r="B12" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,52 +1914,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136361112</v>
+        <v>136689363</v>
       </c>
       <c r="B13" t="n">
-        <v>92123</v>
+        <v>93075</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>4769</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>464689</v>
+        <v>464744</v>
       </c>
       <c r="R13" t="n">
-        <v>6784876</v>
+        <v>6784835</v>
       </c>
       <c r="S13" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1983,22 +1979,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2013,27 +2009,27 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136361112</t>
+          <t>https://artportalen.se/Sighting/136689363</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136361116</v>
+        <v>136361112</v>
       </c>
       <c r="B14" t="n">
-        <v>92123</v>
+        <v>92126</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,13 +2065,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>464581</v>
+        <v>464689</v>
       </c>
       <c r="R14" t="n">
-        <v>6784971</v>
+        <v>6784876</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2104,7 +2100,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2114,7 +2110,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2140,51 +2136,55 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136361116</t>
+          <t>https://artportalen.se/Sighting/136361112</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126330861</v>
+        <v>136361116</v>
       </c>
       <c r="B15" t="n">
-        <v>79327</v>
+        <v>92126</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>464495</v>
+        <v>464581</v>
       </c>
       <c r="R15" t="n">
-        <v>6784979</v>
+        <v>6784971</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2211,12 +2211,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2242,13 +2252,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126330861</t>
+          <t>https://artportalen.se/Sighting/136361116</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126330895</v>
+        <v>126330861</v>
       </c>
       <c r="B16" t="n">
         <v>79327</v>
@@ -2283,10 +2293,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>464517</v>
+        <v>464495</v>
       </c>
       <c r="R16" t="n">
-        <v>6784987</v>
+        <v>6784979</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2344,13 +2354,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126330895</t>
+          <t>https://artportalen.se/Sighting/126330861</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126487034</v>
+        <v>126330895</v>
       </c>
       <c r="B17" t="n">
         <v>79327</v>
@@ -2385,13 +2395,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>464717</v>
+        <v>464517</v>
       </c>
       <c r="R17" t="n">
-        <v>6784886</v>
+        <v>6784987</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2415,27 +2425,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>11:15</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Rikligt i synfältet i en radie av ca 50 meter</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2461,13 +2456,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126487034</t>
+          <t>https://artportalen.se/Sighting/126330895</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126487574</v>
+        <v>126487034</v>
       </c>
       <c r="B18" t="n">
         <v>79327</v>
@@ -2502,13 +2497,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>464728</v>
+        <v>464717</v>
       </c>
       <c r="R18" t="n">
-        <v>6784927</v>
+        <v>6784886</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2548,6 +2543,11 @@
       <c r="AB18" t="inlineStr">
         <is>
           <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Rikligt i synfältet i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2573,13 +2573,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126487574</t>
+          <t>https://artportalen.se/Sighting/126487034</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126487646</v>
+        <v>126487574</v>
       </c>
       <c r="B19" t="n">
         <v>79327</v>
@@ -2614,10 +2614,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>464716</v>
+        <v>464728</v>
       </c>
       <c r="R19" t="n">
-        <v>6784948</v>
+        <v>6784927</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2685,13 +2685,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126487646</t>
+          <t>https://artportalen.se/Sighting/126487574</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126487746</v>
+        <v>126487646</v>
       </c>
       <c r="B20" t="n">
         <v>79327</v>
@@ -2726,13 +2726,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>464684</v>
+        <v>464716</v>
       </c>
       <c r="R20" t="n">
-        <v>6784934</v>
+        <v>6784948</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2772,11 +2772,6 @@
       <c r="AB20" t="inlineStr">
         <is>
           <t>11:15</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2802,13 +2797,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126487746</t>
+          <t>https://artportalen.se/Sighting/126487646</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126487998</v>
+        <v>126487746</v>
       </c>
       <c r="B21" t="n">
         <v>79327</v>
@@ -2843,13 +2838,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>464676</v>
+        <v>464684</v>
       </c>
       <c r="R21" t="n">
-        <v>6784994</v>
+        <v>6784934</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2889,6 +2884,11 @@
       <c r="AB21" t="inlineStr">
         <is>
           <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2914,13 +2914,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126487998</t>
+          <t>https://artportalen.se/Sighting/126487746</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126488129</v>
+        <v>126487998</v>
       </c>
       <c r="B22" t="n">
         <v>79327</v>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>464617</v>
+        <v>464676</v>
       </c>
       <c r="R22" t="n">
-        <v>6785002</v>
+        <v>6784994</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3026,13 +3026,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126488129</t>
+          <t>https://artportalen.se/Sighting/126487998</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126488197</v>
+        <v>126488129</v>
       </c>
       <c r="B23" t="n">
         <v>79327</v>
@@ -3067,10 +3067,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>464601</v>
+        <v>464617</v>
       </c>
       <c r="R23" t="n">
-        <v>6785020</v>
+        <v>6785002</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3138,13 +3138,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126488197</t>
+          <t>https://artportalen.se/Sighting/126488129</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126590840</v>
+        <v>126488197</v>
       </c>
       <c r="B24" t="n">
         <v>79327</v>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>464734</v>
+        <v>464601</v>
       </c>
       <c r="R24" t="n">
-        <v>6784815</v>
+        <v>6785020</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3209,22 +3209,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3250,13 +3250,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126590840</t>
+          <t>https://artportalen.se/Sighting/126488197</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126590850</v>
+        <v>126590840</v>
       </c>
       <c r="B25" t="n">
         <v>79327</v>
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>464724</v>
+        <v>464734</v>
       </c>
       <c r="R25" t="n">
-        <v>6784810</v>
+        <v>6784815</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3362,13 +3362,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126590850</t>
+          <t>https://artportalen.se/Sighting/126590840</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126590867</v>
+        <v>126590850</v>
       </c>
       <c r="B26" t="n">
         <v>79327</v>
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>464730</v>
+        <v>464724</v>
       </c>
       <c r="R26" t="n">
-        <v>6784826</v>
+        <v>6784810</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3474,13 +3474,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126590867</t>
+          <t>https://artportalen.se/Sighting/126590850</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126591007</v>
+        <v>126590867</v>
       </c>
       <c r="B27" t="n">
         <v>79327</v>
@@ -3515,10 +3515,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>464744</v>
+        <v>464730</v>
       </c>
       <c r="R27" t="n">
-        <v>6784847</v>
+        <v>6784826</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3586,13 +3586,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126591007</t>
+          <t>https://artportalen.se/Sighting/126590867</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126591506</v>
+        <v>126591007</v>
       </c>
       <c r="B28" t="n">
         <v>79327</v>
@@ -3627,10 +3627,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>464757</v>
+        <v>464744</v>
       </c>
       <c r="R28" t="n">
-        <v>6784856</v>
+        <v>6784847</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3698,13 +3698,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126591506</t>
+          <t>https://artportalen.se/Sighting/126591007</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126591615</v>
+        <v>126591506</v>
       </c>
       <c r="B29" t="n">
         <v>79327</v>
@@ -3739,10 +3739,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>464711</v>
+        <v>464757</v>
       </c>
       <c r="R29" t="n">
-        <v>6784812</v>
+        <v>6784856</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3810,13 +3810,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126591615</t>
+          <t>https://artportalen.se/Sighting/126591506</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126591669</v>
+        <v>126591615</v>
       </c>
       <c r="B30" t="n">
         <v>79327</v>
@@ -3851,10 +3851,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>464670</v>
+        <v>464711</v>
       </c>
       <c r="R30" t="n">
-        <v>6784832</v>
+        <v>6784812</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3922,13 +3922,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126591669</t>
+          <t>https://artportalen.se/Sighting/126591615</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126592039</v>
+        <v>126591669</v>
       </c>
       <c r="B31" t="n">
         <v>79327</v>
@@ -3963,10 +3963,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>464676</v>
+        <v>464670</v>
       </c>
       <c r="R31" t="n">
-        <v>6784794</v>
+        <v>6784832</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4034,13 +4034,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126592039</t>
+          <t>https://artportalen.se/Sighting/126591669</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126592098</v>
+        <v>126592039</v>
       </c>
       <c r="B32" t="n">
         <v>79327</v>
@@ -4078,7 +4078,7 @@
         <v>464676</v>
       </c>
       <c r="R32" t="n">
-        <v>6784780</v>
+        <v>6784794</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4123,11 +4123,6 @@
           <t>17:39</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Garn vid rullstensås</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4151,13 +4146,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126592098</t>
+          <t>https://artportalen.se/Sighting/126592039</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126601634</v>
+        <v>126592098</v>
       </c>
       <c r="B33" t="n">
         <v>79327</v>
@@ -4192,10 +4187,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>464649</v>
+        <v>464676</v>
       </c>
       <c r="R33" t="n">
-        <v>6784788</v>
+        <v>6784780</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4222,22 +4217,27 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Garn vid rullstensås</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4263,13 +4263,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126601634</t>
+          <t>https://artportalen.se/Sighting/126592098</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126601664</v>
+        <v>126601634</v>
       </c>
       <c r="B34" t="n">
         <v>79327</v>
@@ -4304,10 +4304,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>464646</v>
+        <v>464649</v>
       </c>
       <c r="R34" t="n">
-        <v>6784794</v>
+        <v>6784788</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4375,13 +4375,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126601664</t>
+          <t>https://artportalen.se/Sighting/126601634</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126601674</v>
+        <v>126601664</v>
       </c>
       <c r="B35" t="n">
         <v>79327</v>
@@ -4416,10 +4416,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>464640</v>
+        <v>464646</v>
       </c>
       <c r="R35" t="n">
-        <v>6784813</v>
+        <v>6784794</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4487,13 +4487,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126601674</t>
+          <t>https://artportalen.se/Sighting/126601664</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126601759</v>
+        <v>126601674</v>
       </c>
       <c r="B36" t="n">
         <v>79327</v>
@@ -4528,10 +4528,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>464631</v>
+        <v>464640</v>
       </c>
       <c r="R36" t="n">
-        <v>6784825</v>
+        <v>6784813</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4563,7 +4563,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4599,13 +4599,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126601759</t>
+          <t>https://artportalen.se/Sighting/126601674</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126601794</v>
+        <v>126601759</v>
       </c>
       <c r="B37" t="n">
         <v>79327</v>
@@ -4640,10 +4640,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>464632</v>
+        <v>464631</v>
       </c>
       <c r="R37" t="n">
-        <v>6784828</v>
+        <v>6784825</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4711,13 +4711,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126601794</t>
+          <t>https://artportalen.se/Sighting/126601759</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126601811</v>
+        <v>126601794</v>
       </c>
       <c r="B38" t="n">
         <v>79327</v>
@@ -4752,10 +4752,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>464636</v>
+        <v>464632</v>
       </c>
       <c r="R38" t="n">
-        <v>6784853</v>
+        <v>6784828</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4823,13 +4823,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126601811</t>
+          <t>https://artportalen.se/Sighting/126601794</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126601839</v>
+        <v>126601811</v>
       </c>
       <c r="B39" t="n">
         <v>79327</v>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>464633</v>
+        <v>464636</v>
       </c>
       <c r="R39" t="n">
-        <v>6784875</v>
+        <v>6784853</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4935,13 +4935,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126601839</t>
+          <t>https://artportalen.se/Sighting/126601811</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126601871</v>
+        <v>126601839</v>
       </c>
       <c r="B40" t="n">
         <v>79327</v>
@@ -4976,10 +4976,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>464603</v>
+        <v>464633</v>
       </c>
       <c r="R40" t="n">
-        <v>6784862</v>
+        <v>6784875</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5047,13 +5047,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126601871</t>
+          <t>https://artportalen.se/Sighting/126601839</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126602170</v>
+        <v>126601871</v>
       </c>
       <c r="B41" t="n">
         <v>79327</v>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>464599</v>
+        <v>464603</v>
       </c>
       <c r="R41" t="n">
-        <v>6784887</v>
+        <v>6784862</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5159,13 +5159,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126602170</t>
+          <t>https://artportalen.se/Sighting/126601871</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126602281</v>
+        <v>126602170</v>
       </c>
       <c r="B42" t="n">
         <v>79327</v>
@@ -5200,10 +5200,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>464586</v>
+        <v>464599</v>
       </c>
       <c r="R42" t="n">
-        <v>6784897</v>
+        <v>6784887</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5271,13 +5271,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126602281</t>
+          <t>https://artportalen.se/Sighting/126602170</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126602285</v>
+        <v>126602281</v>
       </c>
       <c r="B43" t="n">
         <v>79327</v>
@@ -5312,10 +5312,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>464576</v>
+        <v>464586</v>
       </c>
       <c r="R43" t="n">
-        <v>6784903</v>
+        <v>6784897</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5383,13 +5383,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126602285</t>
+          <t>https://artportalen.se/Sighting/126602281</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126602311</v>
+        <v>126602285</v>
       </c>
       <c r="B44" t="n">
         <v>79327</v>
@@ -5424,10 +5424,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>464557</v>
+        <v>464576</v>
       </c>
       <c r="R44" t="n">
-        <v>6784931</v>
+        <v>6784903</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5472,11 +5472,6 @@
           <t>08:52</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Miljöbild, torraka i bakgrund</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5500,13 +5495,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126602311</t>
+          <t>https://artportalen.se/Sighting/126602285</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126602457</v>
+        <v>126602311</v>
       </c>
       <c r="B45" t="n">
         <v>79327</v>
@@ -5541,10 +5536,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>464554</v>
+        <v>464557</v>
       </c>
       <c r="R45" t="n">
-        <v>6784937</v>
+        <v>6784931</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5617,13 +5612,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126602457</t>
+          <t>https://artportalen.se/Sighting/126602311</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126602534</v>
+        <v>126602457</v>
       </c>
       <c r="B46" t="n">
         <v>79327</v>
@@ -5658,10 +5653,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>464528</v>
+        <v>464554</v>
       </c>
       <c r="R46" t="n">
-        <v>6784961</v>
+        <v>6784937</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5706,6 +5701,11 @@
           <t>08:52</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Miljöbild, torraka i bakgrund</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5729,13 +5729,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126602534</t>
+          <t>https://artportalen.se/Sighting/126602457</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126602593</v>
+        <v>126602534</v>
       </c>
       <c r="B47" t="n">
         <v>79327</v>
@@ -5770,10 +5770,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>464508</v>
+        <v>464528</v>
       </c>
       <c r="R47" t="n">
-        <v>6784966</v>
+        <v>6784961</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5841,13 +5841,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126602593</t>
+          <t>https://artportalen.se/Sighting/126602534</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126602700</v>
+        <v>126602593</v>
       </c>
       <c r="B48" t="n">
         <v>79327</v>
@@ -5882,10 +5882,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>464491</v>
+        <v>464508</v>
       </c>
       <c r="R48" t="n">
-        <v>6784992</v>
+        <v>6784966</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5930,11 +5930,6 @@
           <t>08:52</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Miljöbild med bandad tall</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5958,13 +5953,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126602700</t>
+          <t>https://artportalen.se/Sighting/126602593</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126602820</v>
+        <v>126602700</v>
       </c>
       <c r="B49" t="n">
         <v>79327</v>
@@ -5999,10 +5994,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>464494</v>
+        <v>464491</v>
       </c>
       <c r="R49" t="n">
-        <v>6785014</v>
+        <v>6784992</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6047,6 +6042,11 @@
           <t>08:52</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Miljöbild med bandad tall</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6070,13 +6070,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126602820</t>
+          <t>https://artportalen.se/Sighting/126602700</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126602970</v>
+        <v>126602820</v>
       </c>
       <c r="B50" t="n">
         <v>79327</v>
@@ -6111,10 +6111,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>464508</v>
+        <v>464494</v>
       </c>
       <c r="R50" t="n">
-        <v>6785019</v>
+        <v>6785014</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6182,13 +6182,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126602970</t>
+          <t>https://artportalen.se/Sighting/126602820</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126603485</v>
+        <v>126602970</v>
       </c>
       <c r="B51" t="n">
         <v>79327</v>
@@ -6223,10 +6223,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>464538</v>
+        <v>464508</v>
       </c>
       <c r="R51" t="n">
-        <v>6785057</v>
+        <v>6785019</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6271,11 +6271,6 @@
           <t>08:52</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Miljöbild med två tallar, garnlav samt torrakor</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6299,13 +6294,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126603485</t>
+          <t>https://artportalen.se/Sighting/126602970</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126636587</v>
+        <v>126603485</v>
       </c>
       <c r="B52" t="n">
         <v>79327</v>
@@ -6334,19 +6329,16 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>464649</v>
+        <v>464538</v>
       </c>
       <c r="R52" t="n">
-        <v>6784894</v>
+        <v>6785057</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6376,18 +6368,32 @@
           <t>2025-07-12</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-07-12</t>
         </is>
       </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Miljöbild med två tallar, garnlav samt torrakor</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6405,13 +6411,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126636587</t>
+          <t>https://artportalen.se/Sighting/126603485</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126636699</v>
+        <v>126636587</v>
       </c>
       <c r="B53" t="n">
         <v>79327</v>
@@ -6449,10 +6455,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>464636</v>
+        <v>464649</v>
       </c>
       <c r="R53" t="n">
-        <v>6784910</v>
+        <v>6784894</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6511,13 +6517,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126636699</t>
+          <t>https://artportalen.se/Sighting/126636587</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126636724</v>
+        <v>126636699</v>
       </c>
       <c r="B54" t="n">
         <v>79327</v>
@@ -6555,10 +6561,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>464637</v>
+        <v>464636</v>
       </c>
       <c r="R54" t="n">
-        <v>6784913</v>
+        <v>6784910</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6617,13 +6623,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126636724</t>
+          <t>https://artportalen.se/Sighting/126636699</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126636748</v>
+        <v>126636724</v>
       </c>
       <c r="B55" t="n">
         <v>79327</v>
@@ -6661,10 +6667,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>464639</v>
+        <v>464637</v>
       </c>
       <c r="R55" t="n">
-        <v>6784929</v>
+        <v>6784913</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6723,13 +6729,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126636748</t>
+          <t>https://artportalen.se/Sighting/126636724</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126636762</v>
+        <v>126636748</v>
       </c>
       <c r="B56" t="n">
         <v>79327</v>
@@ -6770,7 +6776,7 @@
         <v>464639</v>
       </c>
       <c r="R56" t="n">
-        <v>6784932</v>
+        <v>6784929</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6829,13 +6835,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126636762</t>
+          <t>https://artportalen.se/Sighting/126636748</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126636906</v>
+        <v>126636762</v>
       </c>
       <c r="B57" t="n">
         <v>79327</v>
@@ -6873,10 +6879,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>464593</v>
+        <v>464639</v>
       </c>
       <c r="R57" t="n">
-        <v>6785029</v>
+        <v>6784932</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6935,16 +6941,16 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126636906</t>
+          <t>https://artportalen.se/Sighting/126636762</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>136361117</v>
+        <v>126636906</v>
       </c>
       <c r="B58" t="n">
-        <v>79474</v>
+        <v>79327</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6970,19 +6976,22 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>464581</v>
+        <v>464593</v>
       </c>
       <c r="R58" t="n">
-        <v>6784971</v>
+        <v>6785029</v>
       </c>
       <c r="S58" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7006,27 +7015,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>13:58</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i hela anmälan</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7035,6 +7029,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7052,38 +7047,38 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136361117</t>
+          <t>https://artportalen.se/Sighting/126636906</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126487403</v>
+        <v>136361117</v>
       </c>
       <c r="B59" t="n">
-        <v>83307</v>
+        <v>79474</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7093,13 +7088,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>464751</v>
+        <v>464581</v>
       </c>
       <c r="R59" t="n">
-        <v>6784883</v>
+        <v>6784971</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7123,22 +7118,27 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i hela anmälan</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7164,13 +7164,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126487403</t>
+          <t>https://artportalen.se/Sighting/136361117</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126487596</v>
+        <v>126487403</v>
       </c>
       <c r="B60" t="n">
         <v>83307</v>
@@ -7205,10 +7205,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>464738</v>
+        <v>464751</v>
       </c>
       <c r="R60" t="n">
-        <v>6784934</v>
+        <v>6784883</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7276,13 +7276,13 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126487596</t>
+          <t>https://artportalen.se/Sighting/126487403</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127465540</v>
+        <v>126487596</v>
       </c>
       <c r="B61" t="n">
         <v>83307</v>
@@ -7311,19 +7311,16 @@
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>464659</v>
+        <v>464738</v>
       </c>
       <c r="R61" t="n">
-        <v>6785196</v>
+        <v>6784934</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7350,12 +7347,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7364,7 +7371,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7382,16 +7388,16 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127465540</t>
+          <t>https://artportalen.se/Sighting/126487596</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126488269</v>
+        <v>127465540</v>
       </c>
       <c r="B62" t="n">
-        <v>79084</v>
+        <v>83307</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7399,37 +7405,40 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Bjönsaberg, Bjönsaberg, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>464700</v>
+        <v>464659</v>
       </c>
       <c r="R62" t="n">
-        <v>6784944</v>
+        <v>6785196</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7453,22 +7462,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7477,30 +7476,31 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126488269</t>
+          <t>https://artportalen.se/Sighting/127465540</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126488981</v>
+        <v>126488269</v>
       </c>
       <c r="B63" t="n">
         <v>79084</v>
@@ -7531,17 +7531,17 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Kölbron, Dlr</t>
+          <t>Bjönsaberg, Bjönsaberg, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>464546</v>
+        <v>464700</v>
       </c>
       <c r="R63" t="n">
-        <v>6785003</v>
+        <v>6784944</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7580,7 +7580,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7595,24 +7595,24 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126488981</t>
+          <t>https://artportalen.se/Sighting/126488269</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126601627</v>
+        <v>126488981</v>
       </c>
       <c r="B64" t="n">
         <v>79084</v>
@@ -7647,10 +7647,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>464649</v>
+        <v>464546</v>
       </c>
       <c r="R64" t="n">
-        <v>6784788</v>
+        <v>6785003</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7677,22 +7677,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7718,13 +7718,13 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126601627</t>
+          <t>https://artportalen.se/Sighting/126488981</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126602948</v>
+        <v>126601627</v>
       </c>
       <c r="B65" t="n">
         <v>79084</v>
@@ -7759,10 +7759,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>464508</v>
+        <v>464649</v>
       </c>
       <c r="R65" t="n">
-        <v>6785019</v>
+        <v>6784788</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7804,7 +7804,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7830,16 +7830,16 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126602948</t>
+          <t>https://artportalen.se/Sighting/126601627</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126330969</v>
+        <v>126602948</v>
       </c>
       <c r="B66" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7847,21 +7847,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7871,10 +7871,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>464525</v>
+        <v>464508</v>
       </c>
       <c r="R66" t="n">
-        <v>6784977</v>
+        <v>6785019</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7901,12 +7901,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7932,13 +7942,13 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126330969</t>
+          <t>https://artportalen.se/Sighting/126602948</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126488973</v>
+        <v>126330969</v>
       </c>
       <c r="B67" t="n">
         <v>79946</v>
@@ -7973,10 +7983,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>464546</v>
+        <v>464525</v>
       </c>
       <c r="R67" t="n">
-        <v>6785003</v>
+        <v>6784977</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8003,22 +8013,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>11:15</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>11:15</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8044,13 +8044,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126488973</t>
+          <t>https://artportalen.se/Sighting/126330969</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126591818</v>
+        <v>126488973</v>
       </c>
       <c r="B68" t="n">
         <v>79946</v>
@@ -8085,10 +8085,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>464670</v>
+        <v>464546</v>
       </c>
       <c r="R68" t="n">
-        <v>6784832</v>
+        <v>6785003</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8115,22 +8115,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8156,13 +8156,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126591818</t>
+          <t>https://artportalen.se/Sighting/126488973</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126601513</v>
+        <v>126591818</v>
       </c>
       <c r="B69" t="n">
         <v>79946</v>
@@ -8197,13 +8197,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>464648</v>
+        <v>464670</v>
       </c>
       <c r="R69" t="n">
-        <v>6784781</v>
+        <v>6784832</v>
       </c>
       <c r="S69" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8227,22 +8227,22 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8268,13 +8268,13 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126601513</t>
+          <t>https://artportalen.se/Sighting/126591818</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126601621</v>
+        <v>126601513</v>
       </c>
       <c r="B70" t="n">
         <v>79946</v>
@@ -8309,13 +8309,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>464649</v>
+        <v>464648</v>
       </c>
       <c r="R70" t="n">
-        <v>6784788</v>
+        <v>6784781</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8380,13 +8380,13 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126601621</t>
+          <t>https://artportalen.se/Sighting/126601513</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126602950</v>
+        <v>126601621</v>
       </c>
       <c r="B71" t="n">
         <v>79946</v>
@@ -8421,10 +8421,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>464508</v>
+        <v>464649</v>
       </c>
       <c r="R71" t="n">
-        <v>6785019</v>
+        <v>6784788</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8456,7 +8456,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8492,59 +8492,54 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126602950</t>
+          <t>https://artportalen.se/Sighting/126601621</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126487352</v>
+        <v>126602950</v>
       </c>
       <c r="B72" t="n">
-        <v>57950</v>
+        <v>79946</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Bjönsaberg, Bjönsaberg, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>464756</v>
+        <v>464508</v>
       </c>
       <c r="R72" t="n">
-        <v>6784907</v>
+        <v>6785019</v>
       </c>
       <c r="S72" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8568,22 +8563,22 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8598,24 +8593,24 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126487352</t>
+          <t>https://artportalen.se/Sighting/126602950</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126487945</v>
+        <v>126487352</v>
       </c>
       <c r="B73" t="n">
         <v>57950</v>
@@ -8651,17 +8646,17 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Kölbron, Dlr</t>
+          <t>Bjönsaberg, Bjönsaberg, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>464676</v>
+        <v>464756</v>
       </c>
       <c r="R73" t="n">
-        <v>6784994</v>
+        <v>6784907</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8690,7 +8685,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8700,7 +8695,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8715,24 +8710,24 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126487945</t>
+          <t>https://artportalen.se/Sighting/126487352</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126488274</v>
+        <v>126487945</v>
       </c>
       <c r="B74" t="n">
         <v>57950</v>
@@ -8763,7 +8758,7 @@
       <c r="I74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -8772,10 +8767,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>464590</v>
+        <v>464676</v>
       </c>
       <c r="R74" t="n">
-        <v>6785034</v>
+        <v>6784994</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8843,13 +8838,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126488274</t>
+          <t>https://artportalen.se/Sighting/126487945</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126601937</v>
+        <v>126488274</v>
       </c>
       <c r="B75" t="n">
         <v>57950</v>
@@ -8889,10 +8884,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>464603</v>
+        <v>464590</v>
       </c>
       <c r="R75" t="n">
-        <v>6784862</v>
+        <v>6785034</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8919,27 +8914,22 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>08:52</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Miljöbilder på bohål</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8965,13 +8955,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126601937</t>
+          <t>https://artportalen.se/Sighting/126488274</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126602338</v>
+        <v>126601937</v>
       </c>
       <c r="B76" t="n">
         <v>57950</v>
@@ -9002,7 +8992,7 @@
       <c r="I76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -9011,10 +9001,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>464557</v>
+        <v>464603</v>
       </c>
       <c r="R76" t="n">
-        <v>6784931</v>
+        <v>6784862</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9061,7 +9051,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Miljöbild</t>
+          <t>Miljöbilder på bohål</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9087,13 +9077,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126602338</t>
+          <t>https://artportalen.se/Sighting/126601937</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126636895</v>
+        <v>126602338</v>
       </c>
       <c r="B77" t="n">
         <v>57950</v>
@@ -9122,24 +9112,21 @@
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>464593</v>
+        <v>464557</v>
       </c>
       <c r="R77" t="n">
-        <v>6785029</v>
+        <v>6784931</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9169,9 +9156,24 @@
           <t>2025-07-12</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9197,13 +9199,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126636895</t>
+          <t>https://artportalen.se/Sighting/126602338</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126671230</v>
+        <v>126636895</v>
       </c>
       <c r="B78" t="n">
         <v>57950</v>
@@ -9246,10 +9248,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>464649</v>
+        <v>464593</v>
       </c>
       <c r="R78" t="n">
-        <v>6785183</v>
+        <v>6785029</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9307,13 +9309,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126671230</t>
+          <t>https://artportalen.se/Sighting/126636895</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127465306</v>
+        <v>126671230</v>
       </c>
       <c r="B79" t="n">
         <v>57950</v>
@@ -9356,10 +9358,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>464656</v>
+        <v>464649</v>
       </c>
       <c r="R79" t="n">
-        <v>6785173</v>
+        <v>6785183</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9386,12 +9388,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9417,13 +9419,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127465306</t>
+          <t>https://artportalen.se/Sighting/126671230</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127465502</v>
+        <v>127465306</v>
       </c>
       <c r="B80" t="n">
         <v>57950</v>
@@ -9456,7 +9458,7 @@
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
@@ -9466,10 +9468,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>464662</v>
+        <v>464656</v>
       </c>
       <c r="R80" t="n">
-        <v>6785158</v>
+        <v>6785173</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9527,13 +9529,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127465502</t>
+          <t>https://artportalen.se/Sighting/127465306</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127465578</v>
+        <v>127465502</v>
       </c>
       <c r="B81" t="n">
         <v>57950</v>
@@ -9566,7 +9568,7 @@
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
@@ -9576,10 +9578,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>464659</v>
+        <v>464662</v>
       </c>
       <c r="R81" t="n">
-        <v>6785196</v>
+        <v>6785158</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9637,16 +9639,16 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127465578</t>
+          <t>https://artportalen.se/Sighting/127465502</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>136361111</v>
+        <v>127465578</v>
       </c>
       <c r="B82" t="n">
-        <v>57193</v>
+        <v>57950</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9654,42 +9656,45 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>464633</v>
+        <v>464659</v>
       </c>
       <c r="R82" t="n">
-        <v>6784830</v>
+        <v>6785196</v>
       </c>
       <c r="S82" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9713,22 +9718,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>12:10</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>12:10</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9754,33 +9749,33 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136361111</t>
+          <t>https://artportalen.se/Sighting/127465578</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126487696</v>
+        <v>136361111</v>
       </c>
       <c r="B83" t="n">
-        <v>58209</v>
+        <v>57193</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>102980</v>
+        <v>100138</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ladusvala</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hirundo rustica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -9791,7 +9786,7 @@
       <c r="I83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -9800,13 +9795,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>464716</v>
+        <v>464633</v>
       </c>
       <c r="R83" t="n">
-        <v>6784948</v>
+        <v>6784830</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9830,22 +9825,22 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9871,16 +9866,16 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126487696</t>
+          <t>https://artportalen.se/Sighting/136361111</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>136361106</v>
+        <v>126487696</v>
       </c>
       <c r="B84" t="n">
-        <v>58167</v>
+        <v>58209</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9888,21 +9883,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>103021</v>
+        <v>102980</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9917,13 +9912,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>464726</v>
+        <v>464716</v>
       </c>
       <c r="R84" t="n">
-        <v>6784885</v>
+        <v>6784948</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9947,22 +9942,22 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9988,13 +9983,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136361106</t>
+          <t>https://artportalen.se/Sighting/126487696</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>136361114</v>
+        <v>136361106</v>
       </c>
       <c r="B85" t="n">
         <v>58167</v>
@@ -10022,11 +10017,7 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -10038,10 +10029,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>464700</v>
+        <v>464726</v>
       </c>
       <c r="R85" t="n">
-        <v>6784951</v>
+        <v>6784885</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -10073,7 +10064,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10083,7 +10074,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10109,13 +10100,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136361114</t>
+          <t>https://artportalen.se/Sighting/136361106</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>136361124</v>
+        <v>136361114</v>
       </c>
       <c r="B86" t="n">
         <v>58167</v>
@@ -10159,10 +10150,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>464617</v>
+        <v>464700</v>
       </c>
       <c r="R86" t="n">
-        <v>6785006</v>
+        <v>6784951</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -10194,7 +10185,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10204,7 +10195,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10230,38 +10221,38 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136361124</t>
+          <t>https://artportalen.se/Sighting/136361114</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>136361115</v>
+        <v>136361124</v>
       </c>
       <c r="B87" t="n">
-        <v>58162</v>
+        <v>58167</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -10280,10 +10271,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>464593</v>
+        <v>464617</v>
       </c>
       <c r="R87" t="n">
-        <v>6784885</v>
+        <v>6785006</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10315,7 +10306,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10325,7 +10316,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10351,16 +10342,16 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136361115</t>
+          <t>https://artportalen.se/Sighting/136361124</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>136361118</v>
+        <v>136361115</v>
       </c>
       <c r="B88" t="n">
-        <v>58627</v>
+        <v>58162</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10368,27 +10359,31 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>103041</v>
+        <v>103023</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Bergfink</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Fringilla montifringilla</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -10397,10 +10392,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>464567</v>
+        <v>464593</v>
       </c>
       <c r="R88" t="n">
-        <v>6784968</v>
+        <v>6784885</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10432,7 +10427,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10442,7 +10437,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10468,16 +10463,16 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136361118</t>
+          <t>https://artportalen.se/Sighting/136361115</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>136361110</v>
+        <v>136361118</v>
       </c>
       <c r="B89" t="n">
-        <v>58665</v>
+        <v>58627</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10485,21 +10480,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>103046</v>
+        <v>103041</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Gråsiska</t>
+          <t>Bergfink</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Acanthis flammea</t>
+          <t>Fringilla montifringilla</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10514,13 +10509,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>464637</v>
+        <v>464567</v>
       </c>
       <c r="R89" t="n">
-        <v>6784819</v>
+        <v>6784968</v>
       </c>
       <c r="S89" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10549,7 +10544,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10559,7 +10554,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10585,16 +10580,16 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136361110</t>
+          <t>https://artportalen.se/Sighting/136361118</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126330884</v>
+        <v>136361110</v>
       </c>
       <c r="B90" t="n">
-        <v>8455</v>
+        <v>58665</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10602,37 +10597,42 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>106545</v>
+        <v>103046</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Gråsiska</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Acanthis flammea</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>464495</v>
+        <v>464637</v>
       </c>
       <c r="R90" t="n">
-        <v>6784979</v>
+        <v>6784819</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10656,12 +10656,22 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10687,13 +10697,13 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126330884</t>
+          <t>https://artportalen.se/Sighting/136361110</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126487283</v>
+        <v>126330884</v>
       </c>
       <c r="B91" t="n">
         <v>8455</v>
@@ -10722,24 +10732,19 @@
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Bjönsaberg, Bjönsaberg, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>464756</v>
+        <v>464495</v>
       </c>
       <c r="R91" t="n">
-        <v>6784907</v>
+        <v>6784979</v>
       </c>
       <c r="S91" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10763,22 +10768,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>11:58</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>11:58</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10793,24 +10788,24 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126487283</t>
+          <t>https://artportalen.se/Sighting/126330884</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126487777</v>
+        <v>126487283</v>
       </c>
       <c r="B92" t="n">
         <v>8455</v>
@@ -10839,19 +10834,24 @@
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Kölbron, Kölbron, Dlr</t>
+          <t>Bjönsaberg, Bjönsaberg, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>464717</v>
+        <v>464756</v>
       </c>
       <c r="R92" t="n">
-        <v>6784938</v>
+        <v>6784907</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10916,13 +10916,13 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126487777</t>
+          <t>https://artportalen.se/Sighting/126487283</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126487908</v>
+        <v>126487777</v>
       </c>
       <c r="B93" t="n">
         <v>8455</v>
@@ -10950,29 +10950,20 @@
           <t>(Hartig, 1834)</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Kölbron, Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>464652</v>
+        <v>464717</v>
       </c>
       <c r="R93" t="n">
-        <v>6784976</v>
+        <v>6784938</v>
       </c>
       <c r="S93" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11001,7 +10992,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11011,7 +11002,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11037,13 +11028,13 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126487908</t>
+          <t>https://artportalen.se/Sighting/126487777</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126488040</v>
+        <v>126487908</v>
       </c>
       <c r="B94" t="n">
         <v>8455</v>
@@ -11071,20 +11062,29 @@
           <t>(Hartig, 1834)</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Kölbron, Dlr</t>
+          <t>Kölbron, Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>464676</v>
+        <v>464652</v>
       </c>
       <c r="R94" t="n">
-        <v>6784994</v>
+        <v>6784976</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11113,7 +11113,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11123,7 +11123,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11138,24 +11138,24 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126488040</t>
+          <t>https://artportalen.se/Sighting/126487908</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126488330</v>
+        <v>126488040</v>
       </c>
       <c r="B95" t="n">
         <v>8455</v>
@@ -11190,10 +11190,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>464560</v>
+        <v>464676</v>
       </c>
       <c r="R95" t="n">
-        <v>6785003</v>
+        <v>6784994</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11261,13 +11261,13 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126488330</t>
+          <t>https://artportalen.se/Sighting/126488040</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126489147</v>
+        <v>126488330</v>
       </c>
       <c r="B96" t="n">
         <v>8455</v>
@@ -11296,21 +11296,16 @@
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Kölbron, Kölbron, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>464662</v>
+        <v>464560</v>
       </c>
       <c r="R96" t="n">
-        <v>6784965</v>
+        <v>6785003</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11342,7 +11337,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11352,7 +11347,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11367,24 +11362,24 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126489147</t>
+          <t>https://artportalen.se/Sighting/126488330</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126601826</v>
+        <v>126489147</v>
       </c>
       <c r="B97" t="n">
         <v>8455</v>
@@ -11413,16 +11408,21 @@
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Kölbron, Dlr</t>
+          <t>Kölbron, Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>464636</v>
+        <v>464662</v>
       </c>
       <c r="R97" t="n">
-        <v>6784853</v>
+        <v>6784965</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11449,22 +11449,22 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11479,24 +11479,24 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126601826</t>
+          <t>https://artportalen.se/Sighting/126489147</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126602177</v>
+        <v>126601826</v>
       </c>
       <c r="B98" t="n">
         <v>8455</v>
@@ -11531,10 +11531,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>464599</v>
+        <v>464636</v>
       </c>
       <c r="R98" t="n">
-        <v>6784887</v>
+        <v>6784853</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11602,13 +11602,13 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126602177</t>
+          <t>https://artportalen.se/Sighting/126601826</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126602400</v>
+        <v>126602177</v>
       </c>
       <c r="B99" t="n">
         <v>8455</v>
@@ -11643,10 +11643,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>464557</v>
+        <v>464599</v>
       </c>
       <c r="R99" t="n">
-        <v>6784931</v>
+        <v>6784887</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11714,13 +11714,13 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126602400</t>
+          <t>https://artportalen.se/Sighting/126602177</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126602528</v>
+        <v>126602400</v>
       </c>
       <c r="B100" t="n">
         <v>8455</v>
@@ -11755,10 +11755,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>464528</v>
+        <v>464557</v>
       </c>
       <c r="R100" t="n">
-        <v>6784961</v>
+        <v>6784931</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11803,11 +11803,6 @@
           <t>08:52</t>
         </is>
       </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Miljöbild, flera torrakor i bild</t>
-        </is>
-      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
@@ -11831,13 +11826,13 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126602528</t>
+          <t>https://artportalen.se/Sighting/126602400</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126602588</v>
+        <v>126602528</v>
       </c>
       <c r="B101" t="n">
         <v>8455</v>
@@ -11872,10 +11867,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>464508</v>
+        <v>464528</v>
       </c>
       <c r="R101" t="n">
-        <v>6784966</v>
+        <v>6784961</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11920,6 +11915,11 @@
           <t>08:52</t>
         </is>
       </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Miljöbild, flera torrakor i bild</t>
+        </is>
+      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
@@ -11943,13 +11943,13 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126602588</t>
+          <t>https://artportalen.se/Sighting/126602528</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126602799</v>
+        <v>126602588</v>
       </c>
       <c r="B102" t="n">
         <v>8455</v>
@@ -11984,10 +11984,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>464491</v>
+        <v>464508</v>
       </c>
       <c r="R102" t="n">
-        <v>6784992</v>
+        <v>6784966</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12032,11 +12032,6 @@
           <t>08:52</t>
         </is>
       </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Miljöbild med torraka och bandad tall med garnlav bakgrund</t>
-        </is>
-      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
@@ -12060,13 +12055,13 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126602799</t>
+          <t>https://artportalen.se/Sighting/126602588</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126603440</v>
+        <v>126602799</v>
       </c>
       <c r="B103" t="n">
         <v>8455</v>
@@ -12101,10 +12096,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>464529</v>
+        <v>464491</v>
       </c>
       <c r="R103" t="n">
-        <v>6785062</v>
+        <v>6784992</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12151,7 +12146,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Miljöbild på två lågor</t>
+          <t>Miljöbild med torraka och bandad tall med garnlav bakgrund</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12177,13 +12172,13 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126603440</t>
+          <t>https://artportalen.se/Sighting/126602799</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126636650</v>
+        <v>126603440</v>
       </c>
       <c r="B104" t="n">
         <v>8455</v>
@@ -12212,21 +12207,16 @@
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>464649</v>
+        <v>464529</v>
       </c>
       <c r="R104" t="n">
-        <v>6784894</v>
+        <v>6785062</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12256,18 +12246,32 @@
           <t>2025-07-12</t>
         </is>
       </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-07-12</t>
         </is>
       </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Miljöbild på två lågor</t>
+        </is>
+      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -12285,16 +12289,16 @@
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126636650</t>
+          <t>https://artportalen.se/Sighting/126603440</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>136361108</v>
+        <v>126636650</v>
       </c>
       <c r="B105" t="n">
-        <v>8463</v>
+        <v>8455</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12320,24 +12324,24 @@
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>464700</v>
+        <v>464649</v>
       </c>
       <c r="R105" t="n">
-        <v>6784824</v>
+        <v>6784894</v>
       </c>
       <c r="S105" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12361,22 +12365,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>11:53</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>11:53</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12385,6 +12379,7 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -12402,16 +12397,16 @@
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136361108</t>
+          <t>https://artportalen.se/Sighting/126636650</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126486167</v>
+        <v>136361108</v>
       </c>
       <c r="B106" t="n">
-        <v>97989</v>
+        <v>8463</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12419,37 +12414,42 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>221941</v>
+        <v>106545</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>464730</v>
+        <v>464700</v>
       </c>
       <c r="R106" t="n">
-        <v>6784881</v>
+        <v>6784824</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12473,22 +12473,22 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12514,38 +12514,38 @@
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126486167</t>
+          <t>https://artportalen.se/Sighting/136361108</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126330993</v>
+        <v>126486167</v>
       </c>
       <c r="B107" t="n">
-        <v>79085</v>
+        <v>97989</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>228912</v>
+        <v>221941</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12555,10 +12555,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>464525</v>
+        <v>464730</v>
       </c>
       <c r="R107" t="n">
-        <v>6784977</v>
+        <v>6784881</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12585,12 +12585,22 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12616,13 +12626,13 @@
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126330993</t>
+          <t>https://artportalen.se/Sighting/126486167</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126488376</v>
+        <v>126330993</v>
       </c>
       <c r="B108" t="n">
         <v>79085</v>
@@ -12653,14 +12663,14 @@
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Kölbron, Kölbron, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>464662</v>
+        <v>464525</v>
       </c>
       <c r="R108" t="n">
-        <v>6784965</v>
+        <v>6784977</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12687,22 +12697,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12717,24 +12717,24 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126488376</t>
+          <t>https://artportalen.se/Sighting/126330993</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126601626</v>
+        <v>126488376</v>
       </c>
       <c r="B109" t="n">
         <v>79085</v>
@@ -12765,14 +12765,14 @@
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Kölbron, Dlr</t>
+          <t>Kölbron, Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>464649</v>
+        <v>464662</v>
       </c>
       <c r="R109" t="n">
-        <v>6784788</v>
+        <v>6784965</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12799,22 +12799,22 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12829,24 +12829,24 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126601626</t>
+          <t>https://artportalen.se/Sighting/126488376</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126602944</v>
+        <v>126601626</v>
       </c>
       <c r="B110" t="n">
         <v>79085</v>
@@ -12881,10 +12881,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>464508</v>
+        <v>464649</v>
       </c>
       <c r="R110" t="n">
-        <v>6785019</v>
+        <v>6784788</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12916,7 +12916,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12926,12 +12926,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>08:52</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Miljöbild med kolad stubbe, bandad</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12957,16 +12952,16 @@
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126602944</t>
+          <t>https://artportalen.se/Sighting/126601626</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126330962</v>
+        <v>126602944</v>
       </c>
       <c r="B111" t="n">
-        <v>79917</v>
+        <v>79085</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12974,21 +12969,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12998,10 +12993,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>464525</v>
+        <v>464508</v>
       </c>
       <c r="R111" t="n">
-        <v>6784977</v>
+        <v>6785019</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13028,12 +13023,27 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Miljöbild med kolad stubbe, bandad</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13059,13 +13069,13 @@
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126330962</t>
+          <t>https://artportalen.se/Sighting/126602944</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126601623</v>
+        <v>126330962</v>
       </c>
       <c r="B112" t="n">
         <v>79917</v>
@@ -13100,10 +13110,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>464649</v>
+        <v>464525</v>
       </c>
       <c r="R112" t="n">
-        <v>6784788</v>
+        <v>6784977</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13130,22 +13140,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
-        </is>
-      </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>08:25</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>08:25</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13171,16 +13171,16 @@
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126601623</t>
+          <t>https://artportalen.se/Sighting/126330962</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126492848</v>
+        <v>126601623</v>
       </c>
       <c r="B113" t="n">
-        <v>79350</v>
+        <v>79917</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13188,40 +13188,37 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>260591</v>
+        <v>229821</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>464714</v>
+        <v>464649</v>
       </c>
       <c r="R113" t="n">
-        <v>6784906</v>
+        <v>6784788</v>
       </c>
       <c r="S113" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -13245,17 +13242,22 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13264,23 +13266,133 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126601623</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>126492848</v>
+      </c>
+      <c r="B114" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>464714</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6784906</v>
+      </c>
+      <c r="S114" t="n">
+        <v>25</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF114" t="inlineStr"/>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/126492848</t>
         </is>
@@ -13400,6 +13512,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29934-2025 artfynd.xlsx
+++ b/artfynd/A 29934-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ114"/>
+  <dimension ref="A1:AZ115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1453,7 +1453,7 @@
         <v>136361109</v>
       </c>
       <c r="B9" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>136361119</v>
       </c>
       <c r="B10" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>136361120</v>
       </c>
       <c r="B11" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>136361122</v>
       </c>
       <c r="B12" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>136689363</v>
       </c>
       <c r="B13" t="n">
-        <v>93075</v>
+        <v>93076</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>136361112</v>
       </c>
       <c r="B14" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>136361116</v>
       </c>
       <c r="B15" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -9755,38 +9755,42 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>136361111</v>
+        <v>136699229</v>
       </c>
       <c r="B83" t="n">
-        <v>57193</v>
+        <v>58006</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -9795,13 +9799,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>464633</v>
+        <v>464742</v>
       </c>
       <c r="R83" t="n">
-        <v>6784830</v>
+        <v>6784839</v>
       </c>
       <c r="S83" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9825,22 +9829,27 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Troligen hona med unge, födosökande och revirtrummande.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9860,39 +9869,39 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136361111</t>
+          <t>https://artportalen.se/Sighting/136699229</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126487696</v>
+        <v>136361111</v>
       </c>
       <c r="B84" t="n">
-        <v>58209</v>
+        <v>57193</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>102980</v>
+        <v>100138</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ladusvala</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hirundo rustica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -9903,7 +9912,7 @@
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -9912,13 +9921,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>464716</v>
+        <v>464633</v>
       </c>
       <c r="R84" t="n">
-        <v>6784948</v>
+        <v>6784830</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9942,22 +9951,22 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9983,16 +9992,16 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126487696</t>
+          <t>https://artportalen.se/Sighting/136361111</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>136361106</v>
+        <v>126487696</v>
       </c>
       <c r="B85" t="n">
-        <v>58167</v>
+        <v>58209</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10000,21 +10009,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>103021</v>
+        <v>102980</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10029,13 +10038,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>464726</v>
+        <v>464716</v>
       </c>
       <c r="R85" t="n">
-        <v>6784885</v>
+        <v>6784948</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10059,22 +10068,22 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10100,13 +10109,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136361106</t>
+          <t>https://artportalen.se/Sighting/126487696</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>136361114</v>
+        <v>136361106</v>
       </c>
       <c r="B86" t="n">
         <v>58167</v>
@@ -10134,11 +10143,7 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -10150,10 +10155,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>464700</v>
+        <v>464726</v>
       </c>
       <c r="R86" t="n">
-        <v>6784951</v>
+        <v>6784885</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -10185,7 +10190,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10195,7 +10200,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10221,13 +10226,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136361114</t>
+          <t>https://artportalen.se/Sighting/136361106</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>136361124</v>
+        <v>136361114</v>
       </c>
       <c r="B87" t="n">
         <v>58167</v>
@@ -10271,10 +10276,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>464617</v>
+        <v>464700</v>
       </c>
       <c r="R87" t="n">
-        <v>6785006</v>
+        <v>6784951</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10306,7 +10311,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10316,7 +10321,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10342,38 +10347,38 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136361124</t>
+          <t>https://artportalen.se/Sighting/136361114</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>136361115</v>
+        <v>136361124</v>
       </c>
       <c r="B88" t="n">
-        <v>58162</v>
+        <v>58167</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -10392,10 +10397,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>464593</v>
+        <v>464617</v>
       </c>
       <c r="R88" t="n">
-        <v>6784885</v>
+        <v>6785006</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10427,7 +10432,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10437,7 +10442,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10463,16 +10468,16 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136361115</t>
+          <t>https://artportalen.se/Sighting/136361124</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>136361118</v>
+        <v>136361115</v>
       </c>
       <c r="B89" t="n">
-        <v>58627</v>
+        <v>58162</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10480,27 +10485,31 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>103041</v>
+        <v>103023</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Bergfink</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Fringilla montifringilla</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -10509,10 +10518,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>464567</v>
+        <v>464593</v>
       </c>
       <c r="R89" t="n">
-        <v>6784968</v>
+        <v>6784885</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10544,7 +10553,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10554,7 +10563,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10580,16 +10589,16 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136361118</t>
+          <t>https://artportalen.se/Sighting/136361115</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>136361110</v>
+        <v>136361118</v>
       </c>
       <c r="B90" t="n">
-        <v>58665</v>
+        <v>58627</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10597,21 +10606,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>103046</v>
+        <v>103041</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gråsiska</t>
+          <t>Bergfink</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Acanthis flammea</t>
+          <t>Fringilla montifringilla</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10626,13 +10635,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>464637</v>
+        <v>464567</v>
       </c>
       <c r="R90" t="n">
-        <v>6784819</v>
+        <v>6784968</v>
       </c>
       <c r="S90" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10661,7 +10670,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10671,7 +10680,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10697,16 +10706,16 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136361110</t>
+          <t>https://artportalen.se/Sighting/136361118</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126330884</v>
+        <v>136361110</v>
       </c>
       <c r="B91" t="n">
-        <v>8455</v>
+        <v>58665</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10714,37 +10723,42 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>106545</v>
+        <v>103046</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Gråsiska</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Acanthis flammea</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>464495</v>
+        <v>464637</v>
       </c>
       <c r="R91" t="n">
-        <v>6784979</v>
+        <v>6784819</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10768,12 +10782,22 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10799,13 +10823,13 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126330884</t>
+          <t>https://artportalen.se/Sighting/136361110</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126487283</v>
+        <v>126330884</v>
       </c>
       <c r="B92" t="n">
         <v>8455</v>
@@ -10834,24 +10858,19 @@
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Bjönsaberg, Bjönsaberg, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>464756</v>
+        <v>464495</v>
       </c>
       <c r="R92" t="n">
-        <v>6784907</v>
+        <v>6784979</v>
       </c>
       <c r="S92" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10875,22 +10894,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>11:58</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>11:58</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10905,24 +10914,24 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126487283</t>
+          <t>https://artportalen.se/Sighting/126330884</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126487777</v>
+        <v>126487283</v>
       </c>
       <c r="B93" t="n">
         <v>8455</v>
@@ -10951,19 +10960,24 @@
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Kölbron, Kölbron, Dlr</t>
+          <t>Bjönsaberg, Bjönsaberg, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>464717</v>
+        <v>464756</v>
       </c>
       <c r="R93" t="n">
-        <v>6784938</v>
+        <v>6784907</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11028,13 +11042,13 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126487777</t>
+          <t>https://artportalen.se/Sighting/126487283</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126487908</v>
+        <v>126487777</v>
       </c>
       <c r="B94" t="n">
         <v>8455</v>
@@ -11062,29 +11076,20 @@
           <t>(Hartig, 1834)</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Kölbron, Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>464652</v>
+        <v>464717</v>
       </c>
       <c r="R94" t="n">
-        <v>6784976</v>
+        <v>6784938</v>
       </c>
       <c r="S94" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11113,7 +11118,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11123,7 +11128,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11149,13 +11154,13 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126487908</t>
+          <t>https://artportalen.se/Sighting/126487777</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126488040</v>
+        <v>126487908</v>
       </c>
       <c r="B95" t="n">
         <v>8455</v>
@@ -11183,20 +11188,29 @@
           <t>(Hartig, 1834)</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Kölbron, Dlr</t>
+          <t>Kölbron, Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>464676</v>
+        <v>464652</v>
       </c>
       <c r="R95" t="n">
-        <v>6784994</v>
+        <v>6784976</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11225,7 +11239,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11235,7 +11249,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11250,24 +11264,24 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126488040</t>
+          <t>https://artportalen.se/Sighting/126487908</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126488330</v>
+        <v>126488040</v>
       </c>
       <c r="B96" t="n">
         <v>8455</v>
@@ -11302,10 +11316,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>464560</v>
+        <v>464676</v>
       </c>
       <c r="R96" t="n">
-        <v>6785003</v>
+        <v>6784994</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11373,13 +11387,13 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126488330</t>
+          <t>https://artportalen.se/Sighting/126488040</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126489147</v>
+        <v>126488330</v>
       </c>
       <c r="B97" t="n">
         <v>8455</v>
@@ -11408,21 +11422,16 @@
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Kölbron, Kölbron, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>464662</v>
+        <v>464560</v>
       </c>
       <c r="R97" t="n">
-        <v>6784965</v>
+        <v>6785003</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11454,7 +11463,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11464,7 +11473,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11479,24 +11488,24 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126489147</t>
+          <t>https://artportalen.se/Sighting/126488330</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126601826</v>
+        <v>126489147</v>
       </c>
       <c r="B98" t="n">
         <v>8455</v>
@@ -11525,16 +11534,21 @@
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Kölbron, Dlr</t>
+          <t>Kölbron, Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>464636</v>
+        <v>464662</v>
       </c>
       <c r="R98" t="n">
-        <v>6784853</v>
+        <v>6784965</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11561,22 +11575,22 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11591,24 +11605,24 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126601826</t>
+          <t>https://artportalen.se/Sighting/126489147</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126602177</v>
+        <v>126601826</v>
       </c>
       <c r="B99" t="n">
         <v>8455</v>
@@ -11643,10 +11657,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>464599</v>
+        <v>464636</v>
       </c>
       <c r="R99" t="n">
-        <v>6784887</v>
+        <v>6784853</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11714,13 +11728,13 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126602177</t>
+          <t>https://artportalen.se/Sighting/126601826</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126602400</v>
+        <v>126602177</v>
       </c>
       <c r="B100" t="n">
         <v>8455</v>
@@ -11755,10 +11769,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>464557</v>
+        <v>464599</v>
       </c>
       <c r="R100" t="n">
-        <v>6784931</v>
+        <v>6784887</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11826,13 +11840,13 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126602400</t>
+          <t>https://artportalen.se/Sighting/126602177</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126602528</v>
+        <v>126602400</v>
       </c>
       <c r="B101" t="n">
         <v>8455</v>
@@ -11867,10 +11881,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>464528</v>
+        <v>464557</v>
       </c>
       <c r="R101" t="n">
-        <v>6784961</v>
+        <v>6784931</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11915,11 +11929,6 @@
           <t>08:52</t>
         </is>
       </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Miljöbild, flera torrakor i bild</t>
-        </is>
-      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
@@ -11943,13 +11952,13 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126602528</t>
+          <t>https://artportalen.se/Sighting/126602400</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126602588</v>
+        <v>126602528</v>
       </c>
       <c r="B102" t="n">
         <v>8455</v>
@@ -11984,10 +11993,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>464508</v>
+        <v>464528</v>
       </c>
       <c r="R102" t="n">
-        <v>6784966</v>
+        <v>6784961</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12032,6 +12041,11 @@
           <t>08:52</t>
         </is>
       </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Miljöbild, flera torrakor i bild</t>
+        </is>
+      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
@@ -12055,13 +12069,13 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126602588</t>
+          <t>https://artportalen.se/Sighting/126602528</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126602799</v>
+        <v>126602588</v>
       </c>
       <c r="B103" t="n">
         <v>8455</v>
@@ -12096,10 +12110,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>464491</v>
+        <v>464508</v>
       </c>
       <c r="R103" t="n">
-        <v>6784992</v>
+        <v>6784966</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12144,11 +12158,6 @@
           <t>08:52</t>
         </is>
       </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Miljöbild med torraka och bandad tall med garnlav bakgrund</t>
-        </is>
-      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
@@ -12172,13 +12181,13 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126602799</t>
+          <t>https://artportalen.se/Sighting/126602588</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126603440</v>
+        <v>126602799</v>
       </c>
       <c r="B104" t="n">
         <v>8455</v>
@@ -12213,10 +12222,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>464529</v>
+        <v>464491</v>
       </c>
       <c r="R104" t="n">
-        <v>6785062</v>
+        <v>6784992</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12263,7 +12272,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Miljöbild på två lågor</t>
+          <t>Miljöbild med torraka och bandad tall med garnlav bakgrund</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12289,13 +12298,13 @@
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126603440</t>
+          <t>https://artportalen.se/Sighting/126602799</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126636650</v>
+        <v>126603440</v>
       </c>
       <c r="B105" t="n">
         <v>8455</v>
@@ -12324,21 +12333,16 @@
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>464649</v>
+        <v>464529</v>
       </c>
       <c r="R105" t="n">
-        <v>6784894</v>
+        <v>6785062</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12368,18 +12372,32 @@
           <t>2025-07-12</t>
         </is>
       </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-07-12</t>
         </is>
       </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Miljöbild på två lågor</t>
+        </is>
+      </c>
       <c r="AD105" t="b">
         <v>0</v>
       </c>
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -12397,16 +12415,16 @@
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126636650</t>
+          <t>https://artportalen.se/Sighting/126603440</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>136361108</v>
+        <v>126636650</v>
       </c>
       <c r="B106" t="n">
-        <v>8463</v>
+        <v>8455</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12432,24 +12450,24 @@
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>464700</v>
+        <v>464649</v>
       </c>
       <c r="R106" t="n">
-        <v>6784824</v>
+        <v>6784894</v>
       </c>
       <c r="S106" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12473,22 +12491,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>11:53</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>11:53</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12497,6 +12505,7 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -12514,16 +12523,16 @@
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136361108</t>
+          <t>https://artportalen.se/Sighting/126636650</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126486167</v>
+        <v>136361108</v>
       </c>
       <c r="B107" t="n">
-        <v>97989</v>
+        <v>8463</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12531,37 +12540,42 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>221941</v>
+        <v>106545</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>464730</v>
+        <v>464700</v>
       </c>
       <c r="R107" t="n">
-        <v>6784881</v>
+        <v>6784824</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12585,22 +12599,22 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12626,38 +12640,38 @@
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126486167</t>
+          <t>https://artportalen.se/Sighting/136361108</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126330993</v>
+        <v>126486167</v>
       </c>
       <c r="B108" t="n">
-        <v>79085</v>
+        <v>97989</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>228912</v>
+        <v>221941</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12667,10 +12681,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>464525</v>
+        <v>464730</v>
       </c>
       <c r="R108" t="n">
-        <v>6784977</v>
+        <v>6784881</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12697,12 +12711,22 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12728,13 +12752,13 @@
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126330993</t>
+          <t>https://artportalen.se/Sighting/126486167</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126488376</v>
+        <v>126330993</v>
       </c>
       <c r="B109" t="n">
         <v>79085</v>
@@ -12765,14 +12789,14 @@
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Kölbron, Kölbron, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>464662</v>
+        <v>464525</v>
       </c>
       <c r="R109" t="n">
-        <v>6784965</v>
+        <v>6784977</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12799,22 +12823,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12829,24 +12843,24 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126488376</t>
+          <t>https://artportalen.se/Sighting/126330993</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126601626</v>
+        <v>126488376</v>
       </c>
       <c r="B110" t="n">
         <v>79085</v>
@@ -12877,14 +12891,14 @@
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Kölbron, Dlr</t>
+          <t>Kölbron, Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>464649</v>
+        <v>464662</v>
       </c>
       <c r="R110" t="n">
-        <v>6784788</v>
+        <v>6784965</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12911,22 +12925,22 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12941,24 +12955,24 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126601626</t>
+          <t>https://artportalen.se/Sighting/126488376</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126602944</v>
+        <v>126601626</v>
       </c>
       <c r="B111" t="n">
         <v>79085</v>
@@ -12993,10 +13007,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>464508</v>
+        <v>464649</v>
       </c>
       <c r="R111" t="n">
-        <v>6785019</v>
+        <v>6784788</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13028,7 +13042,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -13038,12 +13052,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>08:52</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Miljöbild med kolad stubbe, bandad</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13069,16 +13078,16 @@
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126602944</t>
+          <t>https://artportalen.se/Sighting/126601626</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126330962</v>
+        <v>126602944</v>
       </c>
       <c r="B112" t="n">
-        <v>79917</v>
+        <v>79085</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13086,21 +13095,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -13110,10 +13119,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>464525</v>
+        <v>464508</v>
       </c>
       <c r="R112" t="n">
-        <v>6784977</v>
+        <v>6785019</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13140,12 +13149,27 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Miljöbild med kolad stubbe, bandad</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13171,13 +13195,13 @@
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126330962</t>
+          <t>https://artportalen.se/Sighting/126602944</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126601623</v>
+        <v>126330962</v>
       </c>
       <c r="B113" t="n">
         <v>79917</v>
@@ -13212,10 +13236,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>464649</v>
+        <v>464525</v>
       </c>
       <c r="R113" t="n">
-        <v>6784788</v>
+        <v>6784977</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13242,22 +13266,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
-        </is>
-      </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>08:25</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
-        </is>
-      </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>08:25</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13283,16 +13297,16 @@
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126601623</t>
+          <t>https://artportalen.se/Sighting/126330962</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126492848</v>
+        <v>126601623</v>
       </c>
       <c r="B114" t="n">
-        <v>79350</v>
+        <v>79917</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13300,40 +13314,37 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>260591</v>
+        <v>229821</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>464714</v>
+        <v>464649</v>
       </c>
       <c r="R114" t="n">
-        <v>6784906</v>
+        <v>6784788</v>
       </c>
       <c r="S114" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13357,17 +13368,22 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13376,23 +13392,133 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126601623</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>126492848</v>
+      </c>
+      <c r="B115" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>464714</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6784906</v>
+      </c>
+      <c r="S115" t="n">
+        <v>25</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF115" t="inlineStr"/>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/126492848</t>
         </is>
@@ -13513,6 +13639,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29934-2025 artfynd.xlsx
+++ b/artfynd/A 29934-2025 artfynd.xlsx
@@ -1453,7 +1453,7 @@
         <v>136361109</v>
       </c>
       <c r="B9" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>136361119</v>
       </c>
       <c r="B10" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>136361120</v>
       </c>
       <c r="B11" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>136361122</v>
       </c>
       <c r="B12" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>136689363</v>
       </c>
       <c r="B13" t="n">
-        <v>93076</v>
+        <v>93081</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2029,7 +2029,7 @@
         <v>136361112</v>
       </c>
       <c r="B14" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>136361116</v>
       </c>
       <c r="B15" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         <v>136361117</v>
       </c>
       <c r="B59" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -9758,7 +9758,7 @@
         <v>136699229</v>
       </c>
       <c r="B83" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>136361111</v>
       </c>
       <c r="B84" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10118,7 +10118,7 @@
         <v>136361106</v>
       </c>
       <c r="B86" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10235,7 +10235,7 @@
         <v>136361114</v>
       </c>
       <c r="B87" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10356,7 +10356,7 @@
         <v>136361124</v>
       </c>
       <c r="B88" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         <v>136361115</v>
       </c>
       <c r="B89" t="n">
-        <v>58162</v>
+        <v>58164</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10598,7 +10598,7 @@
         <v>136361118</v>
       </c>
       <c r="B90" t="n">
-        <v>58627</v>
+        <v>58629</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10715,7 +10715,7 @@
         <v>136361110</v>
       </c>
       <c r="B91" t="n">
-        <v>58665</v>
+        <v>58667</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 29934-2025 artfynd.xlsx
+++ b/artfynd/A 29934-2025 artfynd.xlsx
@@ -2014,7 +2014,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 29934-2025 artfynd.xlsx
+++ b/artfynd/A 29934-2025 artfynd.xlsx
@@ -1453,7 +1453,7 @@
         <v>136361109</v>
       </c>
       <c r="B9" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>136361119</v>
       </c>
       <c r="B10" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>136361120</v>
       </c>
       <c r="B11" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>136361122</v>
       </c>
       <c r="B12" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>136689363</v>
       </c>
       <c r="B13" t="n">
-        <v>93081</v>
+        <v>93083</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>136361112</v>
       </c>
       <c r="B14" t="n">
-        <v>92132</v>
+        <v>92134</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>136361116</v>
       </c>
       <c r="B15" t="n">
-        <v>92132</v>
+        <v>92134</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 29934-2025 artfynd.xlsx
+++ b/artfynd/A 29934-2025 artfynd.xlsx
@@ -2014,7 +2014,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 29934-2025 artfynd.xlsx
+++ b/artfynd/A 29934-2025 artfynd.xlsx
@@ -1453,7 +1453,7 @@
         <v>136361109</v>
       </c>
       <c r="B9" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>136361119</v>
       </c>
       <c r="B10" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>136361120</v>
       </c>
       <c r="B11" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>136361122</v>
       </c>
       <c r="B12" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>136689363</v>
       </c>
       <c r="B13" t="n">
-        <v>93083</v>
+        <v>93085</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>136361112</v>
       </c>
       <c r="B14" t="n">
-        <v>92134</v>
+        <v>92136</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>136361116</v>
       </c>
       <c r="B15" t="n">
-        <v>92134</v>
+        <v>92136</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         <v>136361117</v>
       </c>
       <c r="B59" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Håkan Thenander, Birgitta Kvist, Peter Turander, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>

--- a/artfynd/A 29934-2025 artfynd.xlsx
+++ b/artfynd/A 29934-2025 artfynd.xlsx
@@ -1453,7 +1453,7 @@
         <v>136361109</v>
       </c>
       <c r="B9" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>136361119</v>
       </c>
       <c r="B10" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>136361120</v>
       </c>
       <c r="B11" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>136361122</v>
       </c>
       <c r="B12" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>136689363</v>
       </c>
       <c r="B13" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>136361112</v>
       </c>
       <c r="B14" t="n">
-        <v>92136</v>
+        <v>92138</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>136361116</v>
       </c>
       <c r="B15" t="n">
-        <v>92136</v>
+        <v>92138</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         <v>136361117</v>
       </c>
       <c r="B59" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Birgitta Kvist, Peter Turander, Bengt Oldhammer</t>
+          <t>Håkan Thenander, Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>

--- a/artfynd/A 29934-2025 artfynd.xlsx
+++ b/artfynd/A 29934-2025 artfynd.xlsx
@@ -1917,7 +1917,7 @@
         <v>136689363</v>
       </c>
       <c r="B13" t="n">
-        <v>93087</v>
+        <v>93088</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 29934-2025 artfynd.xlsx
+++ b/artfynd/A 29934-2025 artfynd.xlsx
@@ -1917,7 +1917,7 @@
         <v>136689363</v>
       </c>
       <c r="B13" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 29934-2025 artfynd.xlsx
+++ b/artfynd/A 29934-2025 artfynd.xlsx
@@ -1917,7 +1917,7 @@
         <v>136689363</v>
       </c>
       <c r="B13" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 29934-2025 artfynd.xlsx
+++ b/artfynd/A 29934-2025 artfynd.xlsx
@@ -1917,7 +1917,7 @@
         <v>136689363</v>
       </c>
       <c r="B13" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 29934-2025 artfynd.xlsx
+++ b/artfynd/A 29934-2025 artfynd.xlsx
@@ -1917,7 +1917,7 @@
         <v>136689363</v>
       </c>
       <c r="B13" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -9758,7 +9758,7 @@
         <v>136699229</v>
       </c>
       <c r="B83" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 29934-2025 artfynd.xlsx
+++ b/artfynd/A 29934-2025 artfynd.xlsx
@@ -1917,7 +1917,7 @@
         <v>136689363</v>
       </c>
       <c r="B13" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -9758,7 +9758,7 @@
         <v>136699229</v>
       </c>
       <c r="B83" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 29934-2025 artfynd.xlsx
+++ b/artfynd/A 29934-2025 artfynd.xlsx
@@ -9788,11 +9788,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>

--- a/artfynd/A 29934-2025 artfynd.xlsx
+++ b/artfynd/A 29934-2025 artfynd.xlsx
@@ -1917,7 +1917,7 @@
         <v>136689363</v>
       </c>
       <c r="B13" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 29934-2025 artfynd.xlsx
+++ b/artfynd/A 29934-2025 artfynd.xlsx
@@ -9758,7 +9758,7 @@
         <v>136699229</v>
       </c>
       <c r="B83" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
